--- a/output/stock_quant_scores/EQR_info.xlsx
+++ b/output/stock_quant_scores/EQR_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FW2"/>
+  <dimension ref="A1:GA2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1091,230 +1091,250 @@
       </c>
       <c r="ED1" s="1" t="inlineStr">
         <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>dividendDate</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="FQ1" s="1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="FR1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="FS1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="FT1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="FU1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="FV1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="FW1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="FX1" s="1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="FY1" s="1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="FP1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="FQ1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="FR1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="FS1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="FT1" s="1" t="inlineStr">
-        <is>
-          <t>dividendDate</t>
-        </is>
-      </c>
-      <c r="FU1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="FV1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="FW1" s="1" t="inlineStr">
+      <c r="GA1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1445,34 +1465,34 @@
         <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>65.68000000000001</v>
+        <v>63.74</v>
       </c>
       <c r="AE2" t="n">
-        <v>65.47</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="AF2" t="n">
+        <v>63.83</v>
+      </c>
+      <c r="AG2" t="n">
         <v>64.83</v>
       </c>
-      <c r="AG2" t="n">
-        <v>65.715</v>
-      </c>
       <c r="AH2" t="n">
-        <v>65.68000000000001</v>
+        <v>63.74</v>
       </c>
       <c r="AI2" t="n">
-        <v>65.47</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="AJ2" t="n">
+        <v>63.83</v>
+      </c>
+      <c r="AK2" t="n">
         <v>64.83</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>65.715</v>
       </c>
       <c r="AL2" t="n">
         <v>2.77</v>
       </c>
       <c r="AM2" t="n">
-        <v>4.22</v>
+        <v>4.29</v>
       </c>
       <c r="AN2" t="n">
         <v>1758758400</v>
@@ -1487,40 +1507,40 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AR2" t="n">
-        <v>24.526314</v>
+        <v>24.259398</v>
       </c>
       <c r="AS2" t="n">
-        <v>38.603546</v>
+        <v>38.18343</v>
       </c>
       <c r="AT2" t="n">
-        <v>1077143</v>
+        <v>2124473</v>
       </c>
       <c r="AU2" t="n">
-        <v>1077143</v>
+        <v>1751735</v>
       </c>
       <c r="AV2" t="n">
-        <v>2132323</v>
+        <v>2099165</v>
       </c>
       <c r="AW2" t="n">
-        <v>2189290</v>
+        <v>2471600</v>
       </c>
       <c r="AX2" t="n">
-        <v>2189290</v>
+        <v>2471600</v>
       </c>
       <c r="AY2" t="n">
-        <v>65.14</v>
+        <v>62.7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>65.15000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="BA2" t="n">
         <v>2</v>
       </c>
       <c r="BB2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC2" t="n">
-        <v>25675976704</v>
+        <v>25396547584</v>
       </c>
       <c r="BD2" t="n">
         <v>59.41</v>
@@ -1535,19 +1555,19 @@
         <v>12.4375</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.432829999999999</v>
+        <v>8.341056999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>65.21939999999999</v>
+        <v>65.0808</v>
       </c>
       <c r="BJ2" t="n">
-        <v>68.67959999999999</v>
+        <v>68.54215000000001</v>
       </c>
       <c r="BK2" t="n">
         <v>2.735</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.041641288</v>
+        <v>0.042908687</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
@@ -1558,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>34261776384</v>
+        <v>33822593024</v>
       </c>
       <c r="BP2" t="n">
         <v>0.33221</v>
@@ -1570,31 +1590,31 @@
         <v>381898057</v>
       </c>
       <c r="BS2" t="n">
-        <v>5594886</v>
+        <v>5413258</v>
       </c>
       <c r="BT2" t="n">
-        <v>5863757</v>
+        <v>5994861</v>
       </c>
       <c r="BU2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BV2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.0147</v>
+        <v>0.014199999</v>
       </c>
       <c r="BX2" t="n">
         <v>0.00533</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.94275004</v>
+        <v>0.94268</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.34</v>
+        <v>2.81</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.0199</v>
+        <v>0.019199999</v>
       </c>
       <c r="CB2" t="n">
         <v>393561899</v>
@@ -1603,7 +1623,7 @@
         <v>28.925</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.2554884</v>
+        <v>2.230942</v>
       </c>
       <c r="CE2" t="n">
         <v>1735603200</v>
@@ -1635,22 +1655,22 @@
         <v>1002844800</v>
       </c>
       <c r="CN2" t="n">
-        <v>11.253</v>
+        <v>11.108</v>
       </c>
       <c r="CO2" t="n">
-        <v>18.443</v>
+        <v>18.207</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.12647957</v>
+        <v>-0.1333602</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CR2" t="n">
         <v>0.6929999999999999</v>
       </c>
       <c r="CS2" t="n">
-        <v>1750723200</v>
+        <v>1758758400</v>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
@@ -1658,7 +1678,7 @@
         </is>
       </c>
       <c r="CU2" t="n">
-        <v>65.23999999999999</v>
+        <v>64.53</v>
       </c>
       <c r="CV2" t="n">
         <v>81</v>
@@ -1767,7 +1787,7 @@
       </c>
       <c r="EA2" t="inlineStr">
         <is>
-          <t>Nasdaq Real Time Price</t>
+          <t>Delayed Quote</t>
         </is>
       </c>
       <c r="EB2" t="b">
@@ -1780,166 +1800,178 @@
       </c>
       <c r="ED2" t="inlineStr">
         <is>
+          <t>NYQ</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>finmb_28209</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>America/New_York</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>EDT</t>
+        </is>
+      </c>
+      <c r="EH2" t="n">
+        <v>-14400000</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>us_market</t>
+        </is>
+      </c>
+      <c r="EJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>1.23941</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>64.53</v>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EO2" t="n">
+        <v>1758925021</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>1758916802</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>2099165</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>5.119999</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>0.08618076</v>
+      </c>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>59.41 - 78.32</t>
+        </is>
+      </c>
+      <c r="EU2" t="n">
+        <v>-13.790001</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>-0.17607254</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>-13.33602</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>1760054400</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>1754337600</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>1762372800</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>1762372800</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>1754406000</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>1754406000</v>
+      </c>
+      <c r="FD2" t="b">
+        <v>1</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>1.39836</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>46.146915</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>-0.55080414</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>-0.008463389</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>-4.0121536</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>-0.058535565</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO2" t="inlineStr">
+        <is>
+          <t>2.3 - Buy</t>
+        </is>
+      </c>
+      <c r="FP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FQ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>745162200000</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>-0.6043691</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>64.14</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>-0.3899994</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>0.7899969999999999</v>
+      </c>
+      <c r="FW2" t="inlineStr">
+        <is>
+          <t>63.83 - 64.83</t>
+        </is>
+      </c>
+      <c r="FX2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="FY2" t="inlineStr">
+        <is>
           <t>Equity Residential</t>
         </is>
       </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>[{'header': 'Dividend', 'message': 'EQR announced a cash dividend of 0.692 with an ex-date of Sep. 25, 2025', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1758772800000, 'amount': '0.692'}}]</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>1758740039</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>NYQ</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>finmb_28209</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>America/New_York</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>EDT</t>
-        </is>
-      </c>
-      <c r="EK2" t="n">
-        <v>-14400000</v>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>us_market</t>
-        </is>
-      </c>
-      <c r="EM2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EN2" t="inlineStr">
+      <c r="FZ2" t="inlineStr">
         <is>
           <t>Equity Residential</t>
         </is>
       </c>
-      <c r="EO2" t="n">
-        <v>-0.6699185</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>65.23999999999999</v>
-      </c>
-      <c r="EQ2" t="b">
-        <v>1</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>745162200000</v>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="ET2" t="n">
-        <v>1762372800</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>1754406000</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>1754406000</v>
-      </c>
-      <c r="EW2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="EY2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>1.39836</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>46.65465</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>0.020599365</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>0.00031584722</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>-3.4396057</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>-0.05008191</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>15</v>
-      </c>
-      <c r="FG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="FH2" t="inlineStr">
-        <is>
-          <t>2.3 - Buy</t>
-        </is>
-      </c>
-      <c r="FI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FJ2" t="n">
-        <v>-0.44000244</v>
-      </c>
-      <c r="FK2" t="inlineStr">
-        <is>
-          <t>64.83 - 65.715</t>
-        </is>
-      </c>
-      <c r="FL2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="FM2" t="n">
-        <v>2132323</v>
-      </c>
-      <c r="FN2" t="n">
-        <v>5.829998</v>
-      </c>
-      <c r="FO2" t="n">
-        <v>0.0981316</v>
-      </c>
-      <c r="FP2" t="inlineStr">
-        <is>
-          <t>59.41 - 78.32</t>
-        </is>
-      </c>
-      <c r="FQ2" t="n">
-        <v>-13.080002</v>
-      </c>
-      <c r="FR2" t="n">
-        <v>-0.16700718</v>
-      </c>
-      <c r="FS2" t="n">
-        <v>-12.647957</v>
-      </c>
-      <c r="FT2" t="n">
-        <v>1760054400</v>
-      </c>
-      <c r="FU2" t="n">
-        <v>1754337600</v>
-      </c>
-      <c r="FV2" t="n">
-        <v>1762372800</v>
-      </c>
-      <c r="FW2" t="inlineStr"/>
+      <c r="GA2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
